--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -550,7 +550,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1119,7 +1119,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
+    <t>原則subjectを記述すべきだが、対象患者が不明なデバイス観察のケースを考慮し、cardinalityは0..1とする。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1147,7 +1147,7 @@
     <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。【JP Core仕様】未使用</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1732,7 +1732,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
